--- a/PickAndPlace_neopixel-seven-segment-display.xlsx
+++ b/PickAndPlace_neopixel-seven-segment-display.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="228">
   <si>
     <t>Designator</t>
   </si>
@@ -97,7 +97,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>降压型 输入3.8V~32V 输出5V 2A</t>
+    <t>3.8V至32V输入、2A低静态电流同步降压转换器，增强EMI抑制</t>
   </si>
   <si>
     <t>C2071056</t>
@@ -106,42 +106,87 @@
     <t>DIODES(美台)</t>
   </si>
   <si>
-    <t>TSOT-26-6</t>
+    <t>TSOT-23-6</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>DSWB01LHGET</t>
+  </si>
+  <si>
+    <t>SW-TH_DSWB01LHGET</t>
+  </si>
+  <si>
+    <t>94.55mm</t>
+  </si>
+  <si>
+    <t>68.1mm</t>
+  </si>
+  <si>
+    <t>71.91mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>红色宽体1位顶拨插件</t>
+  </si>
+  <si>
+    <t>C126888</t>
+  </si>
+  <si>
+    <t>YE</t>
+  </si>
+  <si>
+    <t>插件,9.9x4mm</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>WS2813B-V5</t>
+  </si>
+  <si>
+    <t>LED-SMD_6P-L5.0-W5.0-TL</t>
+  </si>
+  <si>
+    <t>108mm</t>
+  </si>
+  <si>
+    <t>73.5mm</t>
+  </si>
+  <si>
+    <t>110.4mm</t>
+  </si>
+  <si>
+    <t>71.9mm</t>
+  </si>
+  <si>
+    <t>RGB三色</t>
+  </si>
+  <si>
+    <t>C965558</t>
+  </si>
+  <si>
+    <t>worldsemi</t>
+  </si>
+  <si>
+    <t>SMD5050</t>
   </si>
   <si>
     <t>LED2</t>
   </si>
   <si>
-    <t>WS2813B-V5</t>
-  </si>
-  <si>
-    <t>LED-SMD_6P-L5.0-W5.0-TL</t>
-  </si>
-  <si>
     <t>115.5mm</t>
   </si>
   <si>
-    <t>73.5mm</t>
-  </si>
-  <si>
     <t>117.9mm</t>
   </si>
   <si>
-    <t>71.9mm</t>
-  </si>
-  <si>
-    <t>RGB三色</t>
-  </si>
-  <si>
-    <t>C965558</t>
-  </si>
-  <si>
-    <t>worldsemi</t>
-  </si>
-  <si>
-    <t>SMD5050</t>
-  </si>
-  <si>
     <t>LED3</t>
   </si>
   <si>
@@ -184,6 +229,33 @@
     <t>49.1mm</t>
   </si>
   <si>
+    <t>LED7</t>
+  </si>
+  <si>
+    <t>38.5mm</t>
+  </si>
+  <si>
+    <t>36.1mm</t>
+  </si>
+  <si>
+    <t>LED8</t>
+  </si>
+  <si>
+    <t>30.75mm</t>
+  </si>
+  <si>
+    <t>28.35mm</t>
+  </si>
+  <si>
+    <t>LED9</t>
+  </si>
+  <si>
+    <t>23.25mm</t>
+  </si>
+  <si>
+    <t>20.85mm</t>
+  </si>
+  <si>
     <t>LED10</t>
   </si>
   <si>
@@ -196,6 +268,60 @@
     <t>18.1mm</t>
   </si>
   <si>
+    <t>LED11</t>
+  </si>
+  <si>
+    <t>113.1mm</t>
+  </si>
+  <si>
+    <t>LED12</t>
+  </si>
+  <si>
+    <t>105.6mm</t>
+  </si>
+  <si>
+    <t>LED13</t>
+  </si>
+  <si>
+    <t>100mm</t>
+  </si>
+  <si>
+    <t>101.6mm</t>
+  </si>
+  <si>
+    <t>25.65mm</t>
+  </si>
+  <si>
+    <t>LED14</t>
+  </si>
+  <si>
+    <t>33.15mm</t>
+  </si>
+  <si>
+    <t>LED15</t>
+  </si>
+  <si>
+    <t>40.9mm</t>
+  </si>
+  <si>
+    <t>LED16</t>
+  </si>
+  <si>
+    <t>53.9mm</t>
+  </si>
+  <si>
+    <t>LED17</t>
+  </si>
+  <si>
+    <t>61.4mm</t>
+  </si>
+  <si>
+    <t>LED18</t>
+  </si>
+  <si>
+    <t>68.9mm</t>
+  </si>
+  <si>
     <t>LED19</t>
   </si>
   <si>
@@ -205,100 +331,19 @@
     <t>46.6mm</t>
   </si>
   <si>
-    <t>LED11</t>
-  </si>
-  <si>
-    <t>113.1mm</t>
-  </si>
-  <si>
     <t>LED20</t>
   </si>
   <si>
-    <t>LED12</t>
-  </si>
-  <si>
-    <t>108mm</t>
-  </si>
-  <si>
-    <t>105.6mm</t>
-  </si>
-  <si>
     <t>LED21</t>
   </si>
   <si>
-    <t>LED13</t>
-  </si>
-  <si>
-    <t>100mm</t>
-  </si>
-  <si>
-    <t>23.25mm</t>
-  </si>
-  <si>
-    <t>101.6mm</t>
-  </si>
-  <si>
-    <t>25.65mm</t>
-  </si>
-  <si>
-    <t>LED14</t>
-  </si>
-  <si>
-    <t>30.75mm</t>
-  </si>
-  <si>
-    <t>33.15mm</t>
-  </si>
-  <si>
-    <t>LED15</t>
-  </si>
-  <si>
-    <t>38.5mm</t>
-  </si>
-  <si>
-    <t>40.9mm</t>
-  </si>
-  <si>
-    <t>LED16</t>
-  </si>
-  <si>
-    <t>53.9mm</t>
-  </si>
-  <si>
-    <t>LED17</t>
-  </si>
-  <si>
-    <t>61.4mm</t>
-  </si>
-  <si>
-    <t>LED18</t>
-  </si>
-  <si>
-    <t>68.9mm</t>
-  </si>
-  <si>
-    <t>LED7</t>
-  </si>
-  <si>
-    <t>36.1mm</t>
-  </si>
-  <si>
-    <t>LED8</t>
-  </si>
-  <si>
-    <t>28.35mm</t>
-  </si>
-  <si>
-    <t>LED9</t>
-  </si>
-  <si>
-    <t>20.85mm</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>110.4mm</t>
+    <t>LED22</t>
+  </si>
+  <si>
+    <t>62.5mm</t>
+  </si>
+  <si>
+    <t>64.9mm</t>
   </si>
   <si>
     <t>LED23</t>
@@ -334,73 +379,73 @@
     <t>LED27</t>
   </si>
   <si>
+    <t>LED28</t>
+  </si>
+  <si>
+    <t>LED29</t>
+  </si>
+  <si>
+    <t>LED30</t>
+  </si>
+  <si>
     <t>LED31</t>
   </si>
   <si>
     <t>75.1mm</t>
   </si>
   <si>
+    <t>LED32</t>
+  </si>
+  <si>
+    <t>67.6mm</t>
+  </si>
+  <si>
+    <t>LED33</t>
+  </si>
+  <si>
+    <t>60.1mm</t>
+  </si>
+  <si>
+    <t>LED34</t>
+  </si>
+  <si>
+    <t>54.5mm</t>
+  </si>
+  <si>
+    <t>56.1mm</t>
+  </si>
+  <si>
+    <t>LED35</t>
+  </si>
+  <si>
+    <t>LED36</t>
+  </si>
+  <si>
+    <t>LED37</t>
+  </si>
+  <si>
+    <t>LED38</t>
+  </si>
+  <si>
+    <t>LED39</t>
+  </si>
+  <si>
     <t>LED40</t>
   </si>
   <si>
-    <t>LED32</t>
-  </si>
-  <si>
-    <t>67.6mm</t>
-  </si>
-  <si>
     <t>LED41</t>
   </si>
   <si>
-    <t>LED33</t>
-  </si>
-  <si>
-    <t>62.5mm</t>
-  </si>
-  <si>
-    <t>60.1mm</t>
-  </si>
-  <si>
     <t>LED42</t>
   </si>
   <si>
-    <t>LED34</t>
-  </si>
-  <si>
-    <t>54.5mm</t>
-  </si>
-  <si>
-    <t>56.1mm</t>
-  </si>
-  <si>
-    <t>LED35</t>
-  </si>
-  <si>
-    <t>LED36</t>
-  </si>
-  <si>
-    <t>LED37</t>
-  </si>
-  <si>
-    <t>LED38</t>
-  </si>
-  <si>
-    <t>LED39</t>
-  </si>
-  <si>
-    <t>LED28</t>
-  </si>
-  <si>
-    <t>LED29</t>
-  </si>
-  <si>
-    <t>LED30</t>
-  </si>
-  <si>
-    <t>LED22</t>
-  </si>
-  <si>
-    <t>64.9mm</t>
+    <t>LED43</t>
+  </si>
+  <si>
+    <t>17mm</t>
+  </si>
+  <si>
+    <t>19.4mm</t>
   </si>
   <si>
     <t>LED44</t>
@@ -436,73 +481,157 @@
     <t>LED48</t>
   </si>
   <si>
+    <t>LED49</t>
+  </si>
+  <si>
+    <t>LED50</t>
+  </si>
+  <si>
+    <t>LED51</t>
+  </si>
+  <si>
     <t>LED52</t>
   </si>
   <si>
     <t>29.6mm</t>
   </si>
   <si>
+    <t>LED53</t>
+  </si>
+  <si>
+    <t>22.1mm</t>
+  </si>
+  <si>
+    <t>LED54</t>
+  </si>
+  <si>
+    <t>14.6mm</t>
+  </si>
+  <si>
+    <t>LED55</t>
+  </si>
+  <si>
+    <t>9mm</t>
+  </si>
+  <si>
+    <t>10.6mm</t>
+  </si>
+  <si>
+    <t>LED56</t>
+  </si>
+  <si>
+    <t>LED57</t>
+  </si>
+  <si>
+    <t>LED58</t>
+  </si>
+  <si>
+    <t>LED59</t>
+  </si>
+  <si>
+    <t>LED60</t>
+  </si>
+  <si>
     <t>LED61</t>
   </si>
   <si>
-    <t>LED53</t>
-  </si>
-  <si>
-    <t>22.1mm</t>
-  </si>
-  <si>
     <t>LED62</t>
   </si>
   <si>
-    <t>LED54</t>
-  </si>
-  <si>
-    <t>17mm</t>
-  </si>
-  <si>
-    <t>14.6mm</t>
-  </si>
-  <si>
     <t>LED63</t>
   </si>
   <si>
-    <t>LED55</t>
-  </si>
-  <si>
-    <t>9mm</t>
-  </si>
-  <si>
-    <t>10.6mm</t>
-  </si>
-  <si>
-    <t>LED56</t>
-  </si>
-  <si>
-    <t>LED57</t>
-  </si>
-  <si>
-    <t>LED58</t>
-  </si>
-  <si>
-    <t>LED59</t>
-  </si>
-  <si>
-    <t>LED60</t>
-  </si>
-  <si>
-    <t>LED49</t>
-  </si>
-  <si>
-    <t>LED50</t>
-  </si>
-  <si>
-    <t>LED51</t>
-  </si>
-  <si>
-    <t>LED43</t>
-  </si>
-  <si>
-    <t>19.4mm</t>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>DB2EVC-2.54-6P-GN</t>
+  </si>
+  <si>
+    <t>CONN-TH_6P-P2.54_DIBO_DB2EVC-2.54-6P-GN</t>
+  </si>
+  <si>
+    <t>109.15mm</t>
+  </si>
+  <si>
+    <t>1x6P 2.54mm 排数:1 每排P数:6</t>
+  </si>
+  <si>
+    <t>C2927497</t>
+  </si>
+  <si>
+    <t>DORABO(地博电气)</t>
+  </si>
+  <si>
+    <t>插件,P=2.54mm</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>18.15mm</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CL32B106KAJNNNE</t>
+  </si>
+  <si>
+    <t>C1210</t>
+  </si>
+  <si>
+    <t>73.55mm</t>
+  </si>
+  <si>
+    <t>32.05mm</t>
+  </si>
+  <si>
+    <t>75.067mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>10uF ±10% 25V</t>
+  </si>
+  <si>
+    <t>C39232</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>1206N104J500CT</t>
+  </si>
+  <si>
+    <t>C1206</t>
+  </si>
+  <si>
+    <t>24.4mm</t>
+  </si>
+  <si>
+    <t>74.342mm</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>100nF ±5% 50V</t>
+  </si>
+  <si>
+    <t>C170182</t>
+  </si>
+  <si>
+    <t>Walsin(华新科)</t>
+  </si>
+  <si>
+    <t>1206</t>
   </si>
   <si>
     <t>C3</t>
@@ -511,9 +640,6 @@
     <t>CL32B226KAJNNNE</t>
   </si>
   <si>
-    <t>C1210</t>
-  </si>
-  <si>
     <t>67.85mm</t>
   </si>
   <si>
@@ -532,12 +658,6 @@
     <t>C309062</t>
   </si>
   <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -550,60 +670,6 @@
     <t>65.282mm</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>CL32B106KAJNNNE</t>
-  </si>
-  <si>
-    <t>73.55mm</t>
-  </si>
-  <si>
-    <t>32.05mm</t>
-  </si>
-  <si>
-    <t>75.067mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>10uF ±10% 25V</t>
-  </si>
-  <si>
-    <t>C39232</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>1206N104J500CT</t>
-  </si>
-  <si>
-    <t>C1206</t>
-  </si>
-  <si>
-    <t>24.4mm</t>
-  </si>
-  <si>
-    <t>74.342mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>100nF ±5% 50V</t>
-  </si>
-  <si>
-    <t>C170182</t>
-  </si>
-  <si>
-    <t>Walsin(华新科)</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
@@ -629,87 +695,6 @@
   </si>
   <si>
     <t>muRata(村田)</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>PZ254V-11-02P</t>
-  </si>
-  <si>
-    <t>HDR-TH_2P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>97.5mm</t>
-  </si>
-  <si>
-    <t>96.23mm</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>间距:2.54mm 1x2P 直插 方针</t>
-  </si>
-  <si>
-    <t>C492401</t>
-  </si>
-  <si>
-    <t>XFCN(兴飞)</t>
-  </si>
-  <si>
-    <t>插件,P=2.54mm</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>1770995</t>
-  </si>
-  <si>
-    <t>CONN_1814605</t>
-  </si>
-  <si>
-    <t>24.499mm</t>
-  </si>
-  <si>
-    <t>30.776mm</t>
-  </si>
-  <si>
-    <t>18.249mm</t>
-  </si>
-  <si>
-    <t>32.326mm</t>
-  </si>
-  <si>
-    <t>C7435282</t>
-  </si>
-  <si>
-    <t>277-2090-1-ND</t>
-  </si>
-  <si>
-    <t>Phoenix Contact</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>115.499mm</t>
-  </si>
-  <si>
-    <t>59.026mm</t>
-  </si>
-  <si>
-    <t>109.249mm</t>
-  </si>
-  <si>
-    <t>60.576mm</t>
   </si>
 </sst>
 </file>
@@ -1233,69 +1218,69 @@
         <v>36</v>
       </c>
       <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
         <v>38</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
       </c>
       <c r="L3">
         <v>180</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
         <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
         <v>33</v>
       </c>
       <c r="R3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1310,48 +1295,48 @@
         <v>27</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
         <v>48</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I5" t="s">
         <v>50</v>
@@ -1363,57 +1348,57 @@
         <v>26</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M5" t="s">
         <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1422,57 +1407,57 @@
         <v>26</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M6" t="s">
         <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1487,51 +1472,51 @@
         <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R7" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1540,57 +1525,57 @@
         <v>26</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s">
         <v>27</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
         <v>62</v>
       </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1599,57 +1584,57 @@
         <v>26</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M9" t="s">
         <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R9" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
         <v>64</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" t="s">
-        <v>65</v>
-      </c>
       <c r="I10" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1658,57 +1643,57 @@
         <v>26</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s">
         <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R10" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" t="s">
         <v>62</v>
       </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1717,57 +1702,57 @@
         <v>26</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M11" t="s">
         <v>27</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P11" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1776,57 +1761,57 @@
         <v>26</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M12" t="s">
         <v>27</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P12" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R12" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S12" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="J13">
         <v>6</v>
@@ -1841,51 +1826,51 @@
         <v>27</v>
       </c>
       <c r="N13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q13" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S13" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1894,57 +1879,57 @@
         <v>26</v>
       </c>
       <c r="L14">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M14" t="s">
         <v>27</v>
       </c>
       <c r="N14" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P14" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q14" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R14" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S14" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1953,57 +1938,57 @@
         <v>26</v>
       </c>
       <c r="L15">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M15" t="s">
         <v>27</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P15" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q15" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S15" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>80</v>
-      </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -2018,51 +2003,51 @@
         <v>27</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P16" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q16" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R16" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -2077,51 +2062,51 @@
         <v>27</v>
       </c>
       <c r="N17" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P17" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R17" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S17" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2136,51 +2121,51 @@
         <v>27</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P18" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R18" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S18" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2195,51 +2180,51 @@
         <v>27</v>
       </c>
       <c r="N19" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P19" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R19" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S19" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -2248,57 +2233,57 @@
         <v>26</v>
       </c>
       <c r="L20">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M20" t="s">
         <v>27</v>
       </c>
       <c r="N20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P20" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R20" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S20" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
         <v>90</v>
       </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>47</v>
-      </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2307,57 +2292,57 @@
         <v>26</v>
       </c>
       <c r="L21">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M21" t="s">
         <v>27</v>
       </c>
       <c r="N21" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P21" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R21" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S21" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -2366,57 +2351,57 @@
         <v>26</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M22" t="s">
         <v>27</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P22" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R22" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S22" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2425,57 +2410,57 @@
         <v>26</v>
       </c>
       <c r="L23">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M23" t="s">
         <v>27</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P23" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R23" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S23" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2484,57 +2469,57 @@
         <v>26</v>
       </c>
       <c r="L24">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M24" t="s">
         <v>27</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P24" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q24" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R24" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S24" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2549,48 +2534,48 @@
         <v>27</v>
       </c>
       <c r="N25" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P25" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q25" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R25" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S25" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G26" t="s">
         <v>48</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I26" t="s">
         <v>50</v>
@@ -2602,57 +2587,57 @@
         <v>26</v>
       </c>
       <c r="L26">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M26" t="s">
         <v>27</v>
       </c>
       <c r="N26" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O26" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P26" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q26" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R26" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S26" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H27" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J27">
         <v>6</v>
@@ -2661,57 +2646,57 @@
         <v>26</v>
       </c>
       <c r="L27">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s">
         <v>27</v>
       </c>
       <c r="N27" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P27" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q27" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R27" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S27" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H28" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I28" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2726,51 +2711,51 @@
         <v>27</v>
       </c>
       <c r="N28" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O28" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P28" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q28" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R28" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S28" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F29" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H29" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I29" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -2779,57 +2764,57 @@
         <v>26</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M29" t="s">
         <v>27</v>
       </c>
       <c r="N29" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O29" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P29" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R29" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S29" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H30" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I30" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J30">
         <v>6</v>
@@ -2838,57 +2823,57 @@
         <v>26</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M30" t="s">
         <v>27</v>
       </c>
       <c r="N30" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O30" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P30" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R30" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S30" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I31" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -2897,57 +2882,57 @@
         <v>26</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M31" t="s">
         <v>27</v>
       </c>
       <c r="N31" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P31" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q31" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R31" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S31" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I32" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J32">
         <v>6</v>
@@ -2956,57 +2941,57 @@
         <v>26</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M32" t="s">
         <v>27</v>
       </c>
       <c r="N32" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P32" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q32" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R32" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S32" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I33" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -3015,57 +3000,57 @@
         <v>26</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M33" t="s">
         <v>27</v>
       </c>
       <c r="N33" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P33" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q33" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R33" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S33" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="I34" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -3080,51 +3065,51 @@
         <v>27</v>
       </c>
       <c r="N34" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O34" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q34" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R34" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S34" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G35" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I35" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J35">
         <v>6</v>
@@ -3133,57 +3118,57 @@
         <v>26</v>
       </c>
       <c r="L35">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M35" t="s">
         <v>27</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O35" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P35" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q35" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R35" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S35" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="G36" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="I36" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J36">
         <v>6</v>
@@ -3192,57 +3177,57 @@
         <v>26</v>
       </c>
       <c r="L36">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M36" t="s">
         <v>27</v>
       </c>
       <c r="N36" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O36" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P36" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q36" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R36" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S36" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I37" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J37">
         <v>6</v>
@@ -3257,51 +3242,51 @@
         <v>27</v>
       </c>
       <c r="N37" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O37" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P37" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q37" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R37" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S37" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I38" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J38">
         <v>6</v>
@@ -3316,51 +3301,51 @@
         <v>27</v>
       </c>
       <c r="N38" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O38" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P38" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q38" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R38" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S38" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G39" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H39" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -3375,51 +3360,51 @@
         <v>27</v>
       </c>
       <c r="N39" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O39" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P39" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q39" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R39" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S39" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F40" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H40" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J40">
         <v>6</v>
@@ -3434,51 +3419,51 @@
         <v>27</v>
       </c>
       <c r="N40" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O40" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P40" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q40" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R40" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F41" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G41" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H41" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I41" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J41">
         <v>6</v>
@@ -3487,57 +3472,57 @@
         <v>26</v>
       </c>
       <c r="L41">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s">
         <v>27</v>
       </c>
       <c r="N41" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O41" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P41" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q41" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R41" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S41" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H42" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I42" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -3546,57 +3531,57 @@
         <v>26</v>
       </c>
       <c r="L42">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M42" t="s">
         <v>27</v>
       </c>
       <c r="N42" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O42" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P42" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q42" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R42" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S42" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E43" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G43" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="H43" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -3605,57 +3590,57 @@
         <v>26</v>
       </c>
       <c r="L43">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M43" t="s">
         <v>27</v>
       </c>
       <c r="N43" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O43" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P43" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q43" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R43" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S43" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" t="s">
+        <v>112</v>
+      </c>
+      <c r="E44" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H44" t="s">
         <v>128</v>
       </c>
-      <c r="B44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" t="s">
-        <v>114</v>
-      </c>
-      <c r="E44" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" t="s">
-        <v>114</v>
-      </c>
-      <c r="G44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H44" t="s">
-        <v>129</v>
-      </c>
       <c r="I44" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="J44">
         <v>6</v>
@@ -3664,57 +3649,57 @@
         <v>26</v>
       </c>
       <c r="L44">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M44" t="s">
         <v>27</v>
       </c>
       <c r="N44" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O44" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P44" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q44" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R44" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S44" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" t="s">
+        <v>109</v>
+      </c>
+      <c r="G45" t="s">
+        <v>104</v>
+      </c>
+      <c r="H45" t="s">
         <v>130</v>
       </c>
-      <c r="B45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" t="s">
-        <v>131</v>
-      </c>
-      <c r="G45" t="s">
-        <v>36</v>
-      </c>
-      <c r="H45" t="s">
-        <v>132</v>
-      </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="J45">
         <v>6</v>
@@ -3723,57 +3708,57 @@
         <v>26</v>
       </c>
       <c r="L45">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M45" t="s">
         <v>27</v>
       </c>
       <c r="N45" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O45" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P45" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q45" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R45" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S45" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F46" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G46" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I46" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J46">
         <v>6</v>
@@ -3788,48 +3773,48 @@
         <v>27</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O46" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P46" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q46" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R46" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S46" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
         <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G47" t="s">
         <v>48</v>
       </c>
       <c r="H47" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I47" t="s">
         <v>50</v>
@@ -3841,57 +3826,57 @@
         <v>26</v>
       </c>
       <c r="L47">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M47" t="s">
         <v>27</v>
       </c>
       <c r="N47" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O47" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P47" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q47" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R47" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S47" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F48" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G48" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H48" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J48">
         <v>6</v>
@@ -3900,57 +3885,57 @@
         <v>26</v>
       </c>
       <c r="L48">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M48" t="s">
         <v>27</v>
       </c>
       <c r="N48" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O48" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P48" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q48" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R48" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S48" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D49" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F49" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G49" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H49" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="I49" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J49">
         <v>6</v>
@@ -3965,51 +3950,51 @@
         <v>27</v>
       </c>
       <c r="N49" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O49" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P49" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q49" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R49" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S49" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F50" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H50" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I50" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J50">
         <v>6</v>
@@ -4018,57 +4003,57 @@
         <v>26</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M50" t="s">
         <v>27</v>
       </c>
       <c r="N50" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O50" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P50" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q50" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R50" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S50" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E51" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F51" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G51" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H51" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I51" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J51">
         <v>6</v>
@@ -4077,57 +4062,57 @@
         <v>26</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M51" t="s">
         <v>27</v>
       </c>
       <c r="N51" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O51" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P51" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q51" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R51" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S51" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D52" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F52" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H52" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I52" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J52">
         <v>6</v>
@@ -4136,57 +4121,57 @@
         <v>26</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M52" t="s">
         <v>27</v>
       </c>
       <c r="N52" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O52" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P52" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q52" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R52" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S52" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D53" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="E53" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I53" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="J53">
         <v>6</v>
@@ -4195,57 +4180,57 @@
         <v>26</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M53" t="s">
         <v>27</v>
       </c>
       <c r="N53" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O53" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P53" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q53" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R53" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S53" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C54" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E54" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I54" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J54">
         <v>6</v>
@@ -4254,57 +4239,57 @@
         <v>26</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M54" t="s">
         <v>27</v>
       </c>
       <c r="N54" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P54" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q54" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R54" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S54" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C55" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G55" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="I55" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="J55">
         <v>6</v>
@@ -4319,51 +4304,51 @@
         <v>27</v>
       </c>
       <c r="N55" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O55" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P55" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q55" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R55" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S55" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C56" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F56" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G56" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I56" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J56">
         <v>6</v>
@@ -4372,57 +4357,57 @@
         <v>26</v>
       </c>
       <c r="L56">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M56" t="s">
         <v>27</v>
       </c>
       <c r="N56" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O56" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P56" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q56" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R56" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S56" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F57" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G57" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="I57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J57">
         <v>6</v>
@@ -4431,57 +4416,57 @@
         <v>26</v>
       </c>
       <c r="L57">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M57" t="s">
         <v>27</v>
       </c>
       <c r="N57" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O57" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P57" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q57" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R57" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S57" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="I58" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J58">
         <v>6</v>
@@ -4496,51 +4481,51 @@
         <v>27</v>
       </c>
       <c r="N58" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O58" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P58" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q58" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R58" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S58" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E59" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F59" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G59" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="I59" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J59">
         <v>6</v>
@@ -4555,51 +4540,51 @@
         <v>27</v>
       </c>
       <c r="N59" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O59" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P59" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q59" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R59" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S59" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C60" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E60" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F60" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G60" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H60" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="I60" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J60">
         <v>6</v>
@@ -4614,51 +4599,51 @@
         <v>27</v>
       </c>
       <c r="N60" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O60" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P60" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q60" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R60" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S60" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E61" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F61" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G61" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H61" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="I61" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J61">
         <v>6</v>
@@ -4673,51 +4658,51 @@
         <v>27</v>
       </c>
       <c r="N61" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O61" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P61" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q61" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R61" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S61" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="E62" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F62" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="G62" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H62" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="I62" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J62">
         <v>6</v>
@@ -4726,57 +4711,57 @@
         <v>26</v>
       </c>
       <c r="L62">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M62" t="s">
         <v>27</v>
       </c>
       <c r="N62" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O62" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P62" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q62" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R62" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S62" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D63" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="E63" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F63" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="G63" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H63" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J63">
         <v>6</v>
@@ -4785,57 +4770,57 @@
         <v>26</v>
       </c>
       <c r="L63">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M63" t="s">
         <v>27</v>
       </c>
       <c r="N63" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O63" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P63" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q63" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R63" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S63" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D64" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="F64" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G64" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="H64" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="I64" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J64">
         <v>6</v>
@@ -4844,57 +4829,57 @@
         <v>26</v>
       </c>
       <c r="L64">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M64" t="s">
         <v>27</v>
       </c>
       <c r="N64" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O64" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P64" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q64" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R64" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S64" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" t="s">
+        <v>146</v>
+      </c>
+      <c r="G65" t="s">
+        <v>104</v>
+      </c>
+      <c r="H65" t="s">
         <v>162</v>
       </c>
-      <c r="B65" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" t="s">
-        <v>148</v>
-      </c>
-      <c r="E65" t="s">
-        <v>36</v>
-      </c>
-      <c r="F65" t="s">
-        <v>148</v>
-      </c>
-      <c r="G65" t="s">
-        <v>36</v>
-      </c>
-      <c r="H65" t="s">
-        <v>163</v>
-      </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="J65">
         <v>6</v>
@@ -4903,60 +4888,60 @@
         <v>26</v>
       </c>
       <c r="L65">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M65" t="s">
         <v>27</v>
       </c>
       <c r="N65" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O65" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P65" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q65" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="R65" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="S65" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>175</v>
+      </c>
+      <c r="B66" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" t="s">
+        <v>143</v>
+      </c>
+      <c r="E66" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" t="s">
+        <v>143</v>
+      </c>
+      <c r="G66" t="s">
+        <v>104</v>
+      </c>
+      <c r="H66" t="s">
         <v>164</v>
       </c>
-      <c r="B66" t="s">
-        <v>165</v>
-      </c>
-      <c r="C66" t="s">
-        <v>166</v>
-      </c>
-      <c r="D66" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" t="s">
-        <v>168</v>
-      </c>
-      <c r="F66" t="s">
-        <v>167</v>
-      </c>
-      <c r="G66" t="s">
-        <v>168</v>
-      </c>
-      <c r="H66" t="s">
-        <v>169</v>
-      </c>
       <c r="I66" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K66" t="s">
         <v>26</v>
@@ -4968,160 +4953,160 @@
         <v>27</v>
       </c>
       <c r="N66" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="O66" t="s">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="P66" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="Q66" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="R66" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="S66" t="s">
-        <v>174</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B67" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C67" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D67" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="E67" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="F67" t="s">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="G67" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="H67" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I67" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K67" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N67" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="O67" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="P67" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="Q67" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="R67" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="S67" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B68" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" t="s">
+        <v>178</v>
+      </c>
+      <c r="D68" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" t="s">
+        <v>76</v>
+      </c>
+      <c r="F68" t="s">
+        <v>146</v>
+      </c>
+      <c r="G68" t="s">
+        <v>76</v>
+      </c>
+      <c r="H68" t="s">
+        <v>185</v>
+      </c>
+      <c r="I68" t="s">
+        <v>76</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="K68" t="s">
+        <v>38</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="s">
+        <v>39</v>
+      </c>
+      <c r="N68" t="s">
+        <v>177</v>
+      </c>
+      <c r="O68" t="s">
         <v>180</v>
       </c>
-      <c r="C68" t="s">
-        <v>166</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="P68" t="s">
         <v>181</v>
       </c>
-      <c r="E68" t="s">
+      <c r="Q68" t="s">
+        <v>177</v>
+      </c>
+      <c r="R68" t="s">
         <v>182</v>
       </c>
-      <c r="F68" t="s">
-        <v>181</v>
-      </c>
-      <c r="G68" t="s">
-        <v>182</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="S68" t="s">
         <v>183</v>
-      </c>
-      <c r="I68" t="s">
-        <v>182</v>
-      </c>
-      <c r="J68">
-        <v>2</v>
-      </c>
-      <c r="K68" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68">
-        <v>180</v>
-      </c>
-      <c r="M68" t="s">
-        <v>27</v>
-      </c>
-      <c r="N68" t="s">
-        <v>184</v>
-      </c>
-      <c r="O68" t="s">
-        <v>185</v>
-      </c>
-      <c r="P68" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>180</v>
-      </c>
-      <c r="R68" t="s">
-        <v>173</v>
-      </c>
-      <c r="S68" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>186</v>
+      </c>
+      <c r="B69" t="s">
         <v>187</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>188</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>189</v>
-      </c>
-      <c r="D69" t="s">
-        <v>22</v>
       </c>
       <c r="E69" t="s">
         <v>190</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>189</v>
       </c>
       <c r="G69" t="s">
         <v>190</v>
@@ -5154,7 +5139,7 @@
         <v>194</v>
       </c>
       <c r="Q69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R69" t="s">
         <v>195</v>
@@ -5174,22 +5159,22 @@
         <v>199</v>
       </c>
       <c r="D70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" t="s">
         <v>200</v>
       </c>
-      <c r="E70" t="s">
-        <v>91</v>
-      </c>
       <c r="F70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" t="s">
         <v>200</v>
-      </c>
-      <c r="G70" t="s">
-        <v>91</v>
       </c>
       <c r="H70" t="s">
         <v>201</v>
       </c>
       <c r="I70" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="J70">
         <v>2</v>
@@ -5219,51 +5204,51 @@
         <v>205</v>
       </c>
       <c r="S70" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="D71" t="s">
         <v>209</v>
       </c>
       <c r="E71" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="F71" t="s">
         <v>209</v>
       </c>
       <c r="G71" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="H71" t="s">
+        <v>211</v>
+      </c>
+      <c r="I71" t="s">
         <v>210</v>
-      </c>
-      <c r="I71" t="s">
-        <v>36</v>
       </c>
       <c r="J71">
         <v>2</v>
       </c>
       <c r="K71" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71" t="s">
+        <v>27</v>
+      </c>
+      <c r="N71" t="s">
         <v>212</v>
-      </c>
-      <c r="N71" t="s">
-        <v>207</v>
       </c>
       <c r="O71" t="s">
         <v>213</v>
@@ -5272,131 +5257,131 @@
         <v>214</v>
       </c>
       <c r="Q71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="R71" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="S71" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>215</v>
+      </c>
+      <c r="B72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C72" t="s">
+        <v>188</v>
+      </c>
+      <c r="D72" t="s">
+        <v>216</v>
+      </c>
+      <c r="E72" t="s">
         <v>217</v>
       </c>
-      <c r="B72" t="s">
+      <c r="F72" t="s">
+        <v>216</v>
+      </c>
+      <c r="G72" t="s">
+        <v>217</v>
+      </c>
+      <c r="H72" t="s">
         <v>218</v>
       </c>
-      <c r="C72" t="s">
-        <v>219</v>
-      </c>
-      <c r="D72" t="s">
-        <v>220</v>
-      </c>
-      <c r="E72" t="s">
-        <v>221</v>
-      </c>
-      <c r="F72" t="s">
-        <v>131</v>
-      </c>
-      <c r="G72" t="s">
-        <v>77</v>
-      </c>
-      <c r="H72" t="s">
-        <v>222</v>
-      </c>
       <c r="I72" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="J72">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K72" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
       <c r="M72" t="s">
+        <v>27</v>
+      </c>
+      <c r="N72" t="s">
         <v>212</v>
       </c>
-      <c r="N72" t="s">
-        <v>218</v>
-      </c>
       <c r="O72" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="P72" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="Q72" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="R72" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="S72" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C73" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D73" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E73" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="F73" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="G73" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I73" t="s">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="J73">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K73" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M73" t="s">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="N73" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O73" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P73" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R73" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S73" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
